--- a/CustomModel/specific_scale_syn.xlsx
+++ b/CustomModel/specific_scale_syn.xlsx
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -162,6 +162,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -473,19 +476,19 @@
     <col min="2" max="2" style="9" width="5.719285714285714" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="10" width="5.719285714285714" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="10" width="6.147857142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="5.576428571428571" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="5.576428571428571" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="10" width="5.576428571428571" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="10" width="5.862142857142857" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="10" width="6.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="11" width="5.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="11" width="5.433571428571429" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="10" width="5.433571428571429" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="10" width="5.433571428571429" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="10" width="5.719285714285714" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="10" width="5.576428571428571" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="11" width="6.005" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="11" width="6.005" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="11" width="5.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="11" width="6.005" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="12" width="6.005" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="12" width="5.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="12" width="6.005" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="9" width="5.719285714285714" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
@@ -500,7 +503,7 @@
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -512,10 +515,10 @@
       <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -530,13 +533,13 @@
       <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="2" t="s">
@@ -570,25 +573,15 @@
         <v>1</v>
       </c>
       <c r="B3" s="5"/>
-      <c r="C3" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="D3" s="7">
-        <v>0.96</v>
-      </c>
-      <c r="E3" s="7">
-        <v>1.65</v>
-      </c>
-      <c r="F3" s="6">
-        <v>7</v>
-      </c>
-      <c r="G3" s="7">
-        <v>1.2</v>
-      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="K3" s="7"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
@@ -602,23 +595,15 @@
         <v>2</v>
       </c>
       <c r="B4" s="5"/>
-      <c r="C4" s="7">
-        <v>0.93</v>
-      </c>
-      <c r="D4" s="7">
-        <v>9.6</v>
-      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0</v>
-      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="K4" s="7"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
@@ -632,19 +617,11 @@
         <v>3</v>
       </c>
       <c r="B5" s="5"/>
-      <c r="C5" s="7">
-        <v>1.44</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7">
-        <v>4.4</v>
-      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
+      <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
@@ -662,25 +639,15 @@
         <v>4</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="C6" s="7">
-        <v>2.2</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0.96</v>
-      </c>
-      <c r="E6" s="6">
-        <v>8</v>
-      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
+      <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
-      <c r="K6" s="7">
-        <v>0.5</v>
-      </c>
+      <c r="K6" s="7"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
@@ -698,14 +665,10 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="7">
-        <v>1.3</v>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6">
-        <v>5</v>
-      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
@@ -724,18 +687,10 @@
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="7">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6">
-        <v>1</v>
-      </c>
-      <c r="I8" s="7">
-        <v>1</v>
-      </c>
-      <c r="J8" s="6">
-        <v>15</v>
-      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
@@ -754,18 +709,10 @@
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
-      <c r="G9" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="H9" s="7">
-        <v>1</v>
-      </c>
-      <c r="I9" s="7">
-        <v>3</v>
-      </c>
-      <c r="J9" s="6">
-        <v>0</v>
-      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
@@ -784,18 +731,10 @@
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="H10" s="7">
-        <v>1</v>
-      </c>
-      <c r="I10" s="6">
-        <v>5</v>
-      </c>
-      <c r="J10" s="6">
-        <v>0</v>
-      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -810,27 +749,17 @@
         <v>9</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="7">
-        <v>0.6</v>
-      </c>
+      <c r="C11" s="7"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="7">
-        <v>0.6</v>
-      </c>
+      <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-      <c r="K11" s="7">
-        <v>0.6</v>
-      </c>
-      <c r="L11" s="7">
-        <v>1</v>
-      </c>
-      <c r="M11" s="7">
-        <v>2</v>
-      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
@@ -842,28 +771,18 @@
         <v>10</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="7">
-        <v>0.6</v>
-      </c>
+      <c r="C12" s="7"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="7">
-        <v>0.6</v>
-      </c>
+      <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="7">
-        <v>2</v>
-      </c>
-      <c r="L12" s="6">
-        <v>10</v>
-      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="6"/>
       <c r="M12" s="6"/>
-      <c r="N12" s="6">
-        <v>5</v>
-      </c>
+      <c r="N12" s="7"/>
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -874,27 +793,17 @@
         <v>11</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="7">
-        <v>0.6</v>
-      </c>
+      <c r="C13" s="7"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
-      <c r="G13" s="7">
-        <v>0.6</v>
-      </c>
+      <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="L13" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="M13" s="7">
-        <v>2</v>
-      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
@@ -910,21 +819,13 @@
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
-      <c r="G14" s="7">
-        <v>0.8</v>
-      </c>
+      <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="L14" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="M14" s="7">
-        <v>3</v>
-      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
@@ -940,24 +841,16 @@
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
-      <c r="G15" s="7">
-        <v>0.5</v>
-      </c>
+      <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
-      <c r="K15" s="7">
-        <v>0.5</v>
-      </c>
+      <c r="K15" s="7"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
-      <c r="O15" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="P15" s="7">
-        <v>0.8</v>
-      </c>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
       <c r="Q15" s="6"/>
       <c r="R15" s="5"/>
     </row>
@@ -978,15 +871,9 @@
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
-      <c r="O16" s="6">
-        <v>1</v>
-      </c>
-      <c r="P16" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>2</v>
-      </c>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="6"/>
       <c r="R16" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25">
@@ -1006,18 +893,12 @@
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
-      <c r="O17" s="6">
-        <v>1</v>
-      </c>
-      <c r="P17" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>2</v>
-      </c>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="6"/>
       <c r="R17" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="21">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
@@ -1034,15 +915,9 @@
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
-      <c r="O18" s="6">
-        <v>1</v>
-      </c>
-      <c r="P18" s="6">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>2</v>
-      </c>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="6"/>
       <c r="R18" s="5"/>
     </row>
   </sheetData>
